--- a/N30_details.xlsx
+++ b/N30_details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dinguyen/Desktop/Local Documents/GitHub/Paper5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD629E2-2838-6C46-ACC2-149B16884673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E12100-D1FB-774C-9CED-EBA572F0DAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17540" yWindow="760" windowWidth="12700" windowHeight="17340" xr2:uid="{F8F50E29-6092-1842-BA74-444EDD3FCA50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="13">
   <si>
     <t>x verify results</t>
   </si>
@@ -572,11 +572,14 @@
       <c r="J6">
         <v>2</v>
       </c>
+      <c r="K6" t="s">
+        <v>8</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="2" t="str">
+      <c r="N6" s="2">
         <f>IFERROR(IF(K6="y", 0,(L6-M6)/L6),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -595,11 +598,14 @@
       <c r="J7">
         <v>6</v>
       </c>
+      <c r="K7" t="s">
+        <v>8</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="2" t="str">
+      <c r="N7" s="2">
         <f t="shared" ref="N7:N15" si="0">IFERROR(IF(K7="y", 0,(L7-M7)/L7),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -621,9 +627,12 @@
       <c r="J8">
         <v>7</v>
       </c>
-      <c r="N8" s="2" t="str">
+      <c r="K8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -642,8 +651,14 @@
       <c r="J9">
         <v>10</v>
       </c>
+      <c r="L9">
+        <v>323</v>
+      </c>
+      <c r="M9">
+        <v>323</v>
+      </c>
       <c r="N9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(K9="y", 0,(#REF!-#REF!)/#REF!),"")</f>
         <v/>
       </c>
     </row>
@@ -663,9 +678,12 @@
       <c r="J10">
         <v>13</v>
       </c>
-      <c r="N10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="K10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="2">
+        <f>IFERROR(IF(K10="y", 0,(L9-M9)/L9),"")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -684,12 +702,15 @@
       <c r="J11">
         <v>14</v>
       </c>
-      <c r="N11" s="2" t="str">
+      <c r="K11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -705,9 +726,15 @@
       <c r="J12">
         <v>15</v>
       </c>
-      <c r="N12" s="2" t="str">
+      <c r="L12" s="1">
+        <v>212.830274132547</v>
+      </c>
+      <c r="M12" s="1">
+        <v>212.830274132547</v>
+      </c>
+      <c r="N12" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -726,9 +753,15 @@
       <c r="J13">
         <v>16</v>
       </c>
-      <c r="N13" s="2" t="str">
+      <c r="L13">
+        <v>153</v>
+      </c>
+      <c r="M13">
+        <v>153</v>
+      </c>
+      <c r="N13" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -747,9 +780,12 @@
       <c r="J14">
         <v>17</v>
       </c>
-      <c r="N14" s="2" t="str">
+      <c r="K14" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -768,9 +804,15 @@
       <c r="J15">
         <v>21</v>
       </c>
-      <c r="N15" s="2" t="str">
+      <c r="L15">
+        <v>88</v>
+      </c>
+      <c r="M15">
+        <v>88</v>
+      </c>
+      <c r="N15" s="2">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
